--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:45</t>
+    <t xml:space="preserve">2026-09-24 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>7</v>
@@ -570,10 +570,10 @@
         <v>-0.11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="3">
@@ -584,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>7</v>
@@ -593,7 +593,7 @@
         <v>-0.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.07</v>
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>7</v>
@@ -616,10 +616,10 @@
         <v>-0.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>7</v>
@@ -639,10 +639,10 @@
         <v>0.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>7</v>
@@ -662,10 +662,10 @@
         <v>0.23</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="7">
@@ -676,19 +676,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -703,10 +703,10 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -722,10 +722,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -737,7 +737,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>7</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="11">
@@ -760,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>7</v>
@@ -769,10 +769,10 @@
         <v>0.01</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="12">
@@ -783,16 +783,16 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.19</v>
@@ -806,19 +806,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="14">
@@ -835,13 +835,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15">
@@ -852,19 +852,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-0.07</v>
       </c>
     </row>
     <row r="16">
@@ -875,19 +875,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>7</v>
@@ -907,7 +907,7 @@
         <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.22</v>
@@ -927,13 +927,13 @@
         <v>6</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="19">
@@ -950,13 +950,13 @@
         <v>6</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="20">
@@ -967,7 +967,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>6</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="21">
@@ -990,19 +990,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.37</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="22">
@@ -1013,7 +1013,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>7</v>
@@ -1022,10 +1022,10 @@
         <v>-0.06</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="23">
@@ -1036,19 +1036,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.88</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:34</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
